--- a/_Inbox/_Conflicts/LexFlow_Rollout_Tracker.xlsx
+++ b/_Inbox/_Conflicts/LexFlow_Rollout_Tracker.xlsx
@@ -8,6 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project_Roadmap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delegation_Tracking" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contact_Model" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions_Log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elisa_Rollout_Plan" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,13 +59,34 @@
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6E0B4"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -74,13 +101,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -155,6 +197,121 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10001250" cy="7334250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RosterTable" displayName="RosterTable" ref="B5:G19" headerRowCount="1">
+  <autoFilter ref="B5:G19"/>
+  <tableColumns count="6">
+    <tableColumn id="2" name="Name"/>
+    <tableColumn id="3" name="Category"/>
+    <tableColumn id="4" name="Role"/>
+    <tableColumn id="5" name="Status"/>
+    <tableColumn id="6" name="Workspace ID"/>
+    <tableColumn id="7" name="Access / Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DelegationTable" displayName="DelegationTable" ref="B9:G22" headerRowCount="1">
+  <autoFilter ref="B9:G22"/>
+  <tableColumns count="6">
+    <tableColumn id="2" name="Task / Fix"/>
+    <tableColumn id="3" name="Assigned To"/>
+    <tableColumn id="4" name="Status"/>
+    <tableColumn id="5" name="Local Link / Deploy URL"/>
+    <tableColumn id="6" name="Tested On (workspaces)"/>
+    <tableColumn id="7" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="InternalContactsTable" displayName="InternalContactsTable" ref="B10:E19" headerRowCount="1">
+  <autoFilter ref="B10:E19"/>
+  <tableColumns count="4">
+    <tableColumn id="2" name="Field"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Required"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="ClientContactsTable" displayName="ClientContactsTable" ref="B23:E34" headerRowCount="1">
+  <autoFilter ref="B23:E34"/>
+  <tableColumns count="4">
+    <tableColumn id="2" name="Field"/>
+    <tableColumn id="3" name="Type"/>
+    <tableColumn id="4" name="Required"/>
+    <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="DecisionsTable" displayName="DecisionsTable" ref="B5:E16" headerRowCount="1">
+  <autoFilter ref="B5:E16"/>
+  <tableColumns count="4">
+    <tableColumn id="2" name="Decision Item"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Decision / Answer"/>
+    <tableColumn id="5" name="Rationale / Next Step"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="ElisaStagesTable" displayName="ElisaStagesTable" ref="B10:E15" headerRowCount="1">
+  <autoFilter ref="B10:E15"/>
+  <tableColumns count="4">
+    <tableColumn id="2" name="Stage"/>
+    <tableColumn id="3" name="Data Access"/>
+    <tableColumn id="4" name="Approval Gate"/>
+    <tableColumn id="5" name="Test Method"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -446,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C19"/>
+  <dimension ref="B2:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -464,7 +621,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-09-03 | Owner: Olesia Rasing | v2 — surgical update</t>
+          <t>Generated: 2026-09-03 | Owner: Olesia Rasing</t>
         </is>
       </c>
     </row>
@@ -495,7 +652,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Global rules + delegated tasks + Parallel Tracking board</t>
+          <t>Global rule set + delegated tasks (backend-dev, QA, memory-curator)</t>
         </is>
       </c>
     </row>
@@ -526,26 +683,26 @@
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Elisa_Access_Plan</t>
+          <t>Elisa_Rollout_Plan</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>4-phase gated access plan for Elisa integration (Stefano)</t>
+          <t>Sandbox-to-production staged plan for Elisa (LexFlow PA agent)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Key Open Decisions</t>
+          <t>Key Open Decisions (see Decisions_Log for full detail)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>• Matters (cases) per tenant: UNLIMITED for now — tracking mechanism TBD.</t>
+          <t>• Matters (cases) per tenant: UNLIMITED for now — tracking mechanism TBD (see Decisions_Log).</t>
         </is>
       </c>
     </row>
@@ -559,14 +716,14 @@
     <row r="16" ht="18" customHeight="1">
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>• Seat limit per tenant: DECIDED = 5 seats/tenant, starting now. Reconfigurable later via config value.</t>
+          <t>• Seat limit per tenant: SMALL limit approved as starting point — exact number pending research.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>• Elisa (LexFlow PA agent): 4-phase gated plan approved (Sandbox→Read-Only→Staging→Production). See Elisa_Access_Plan sheet.</t>
+          <t>• Elisa (LexFlow PA agent): built, isolated sandbox, NO production data access until explicit approval.</t>
         </is>
       </c>
     </row>
@@ -574,13 +731,6 @@
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>• Internal vs client-facing contacts: approved as TWO separate models — implementation plan pending backend-dev proposal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>• QASkills.sh: verified safe, APPROVED to install now (see Delegation_Tracking).</t>
         </is>
       </c>
     </row>
@@ -594,4 +744,2193 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Project Roadmap — Step Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>For Olesia and delegated agents (Hermes, backend-dev, Elisa)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Roster — People, Testing Customers, AI Agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Status, workspace mapping, access scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Workspace ID</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Access / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Olesia (you)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Superadmin</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>ws7 (LexFlow)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Full access all tenants</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Romanelli Studio</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Testing customer</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Law firm tenant</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Active, live</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>ws10 + cl1, cl2 (client-of-client external clients)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Need to ADD internal users (lawyers/assistant/office) — separate internal contact model required, see Contact_Model sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Pagliano</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Testing customer</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Law firm tenant</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Active, live</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>ws9</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Tommaso Ferro</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Testing customer</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Law firm tenant</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Listed, workspace exists (like AVIBE Agency &amp; aLEXy)</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Workspace ID exists — website not linked yet, not tested yet</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>ASK HERMES: confirm exact workspace ID + link status in inventory table</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>AVIBE Agency</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Testing customer</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Tenant</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Workspace exists, not tested</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>TBD — ask Hermes to confirm</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Website not linked yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>aLEXy</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Testing customer / own product</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Tenant</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Workspace exists, not tested</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>TBD — ask Hermes to confirm</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Website not linked yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Dima</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Collaborator</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Backend developer</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Partially wired</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>LexFlow (ws7) — role scope pending</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Needs separate access inside LexFlow; audits + fixes; add to Delegation_Tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Kirill</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Collaborator</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Design &amp; content creation</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Not yet wired</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>LexFlow (ws7) — Kanban only</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Should see action titles only (not internal notes) in shared LexFlow Kanban</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Stefano</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Collaborator</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>AI agent integration</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Active — building Elisa</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Isolated sandbox (no tenant data)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Building Elisa (LexFlow PA); see Elisa_Rollout_Plan sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Elisa</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Personal LexFlow-legal-CRM assistant (LexFlow PA)</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Built, sandboxed</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Fully isolated sandbox — NO real tenant data access</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>See Elisa_Rollout_Plan for staged go-live logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>backend-dev (AI agent)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Backend audits, cron tasks</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Already running</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Cross-tenant (read/audit scope)</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Already executing scheduled/cron + audit tasks per Delegation_Tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer (Hermes)</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Central orchestrator</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Already running</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Cross-tenant (full deploy scope)</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Executes all deploys/fixes; gated by explicit approval per rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>QA/Test-Debug Agent (proposed)</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Test generation + evidence-based debugging</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Not yet installed — proposed</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>See Delegation_Tracking for skill links (QASkills.sh + debug skill)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Memory-Curator Agent (proposed)</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>AI Agent</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Curates/archives Obsidian vault + skill profiles</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Not yet installed — proposed</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>To be delegated by Operator-Installer; see Delegation_Tracking</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Delegation Tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Global rules apply to ALL future deploys, not just-this-once</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>GLOBAL RULE (confirmed permanent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Any 'fixed'/'done' report must state explicitly: (a) LOCAL — not deployed, with a direct clickable preview link, OR (b) DEPLOYED — with live/staging URL + commit hash. Never state 'fixed' without one of these two. This rule is GLOBAL, applies to every future deploy, not a one-time exception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Task / Fix</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Assigned To</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Local Link / Deploy URL</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Tested On (workspaces)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Backend-dev report review</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>Wait for clean report FIRST. If clean → request local link. If bugs found → audit weak spots first, only then commit+deploy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Intake name field manual entry</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>ws7, ws9, ws10+cl1+cl2</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>Must allow manual override of autofill</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>New contact from intake → appears in Contacts</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>ws7, ws9, ws10+cl1+cl2</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Cross-section reflection requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Cross-section data reflection (Contacts/Calendar/Kanban/Cases)</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>All active tenants</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Test each section individually, report per-tenant not generic PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>RLS merge (feat/rls)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>On hold</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>REMINDER before merge: run 18 tests on real Postgres + confirm NOBYPASSRLS on Railway DATABASE_URL role. Do not merge until both confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Seat limit research + proposal</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>Research small-firm norms (e.g. 3-5 seats), propose number, get sign-off before implementing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Internal vs client-facing contact model design</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>backend-dev</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Pending — approval required before code</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Romanelli first</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Approve table structure, then request implementation plan before Operator-Installer codes it</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Contacts redesign (HubSpot/Salesforce/Clio-style table)</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer + Kirill</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Romanelli first, then replicate</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Table view, status field, bulk-action ready (marketing/email). Isolated frontend feature, can start in parallel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Agentic AI-personalized email automation</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>NOT YET IN PLAN — new item</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Missing from current backlog. Needs own spec: trigger logic + template engine + Resend integration + per-contact personalization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>QA / Test-Debug Agent</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Proposed, not installed</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>https://qaskills.sh</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>QASkills.sh — install via npx @qaskills/cli add &lt;skill&gt;. Complementary: standalone 'debug' skill (hypothesize-then-test workflow) by Ronnie Schaniel — enforces reproduction test before fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Memory-Curator Agent</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Proposed, not installed</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Delegate to a memory-curator agent to save tester/debugger profile + skills into Obsidian vault + working folders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Elisa sandbox → production staging</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Stefano + Operator-Installer</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>In sandbox, isolated</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>N/A — isolated dev env</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>None yet — no real tenant data access</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>See Elisa_Rollout_Plan sheet for staged criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Congestion tracking (matters + memory, unlimited for now)</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Operator-Installer</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Pending — mechanism needed</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Matters/case count + memory/storage per tenant: unlimited for now. Hermes must propose HOW to monitor usage (dashboard/alerts) and AT WHAT THRESHOLD limits get set.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Contact Model — Internal vs Client-Facing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Best-practice field sets, approved as TWO separate models</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Logic Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Romanelli admin/paralegal needs visibility into BOTH: (1) their own internal staff directory (lawyers, assistants, office phone) — NOT client-facing, and (2) client-facing contacts including the client-of-client's own contacts. These are separate data models filtered by workspace_id, not one shared table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Model A — Internal Contacts (Staff Directory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Role/Title</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Lawyer, Paralegal, Assistant, Office Manager</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Office Phone</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Shared/desk line</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Direct Phone</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Personal/mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Email (internal)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Firm domain email</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Workspace ID</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Filters visibility to Romanelli ws10 only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Employment Status</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Active / On leave / Departed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Bar/License Number</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>For lawyers only, legal compliance field</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Visible To</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Multi-select</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Admin, Paralegal roles (not client-facing users)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Model B — Client-Facing Contacts (Marketing-Ready)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Full Name / Company Name</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Person or entity</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Contact Type</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Individual / Client-of-client / Organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Primary marketing/comm channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Case/Matter Link</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Links to active case(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Lifecycle Stage</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Lead / Active / Passive / Closed (per earlier decision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Marketing Consent</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>GDPR — required for EU clients (Italy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Tags/Segments</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Multi-select</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>For bulk email targeting/segmentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Last Contacted</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>Auto-updated, used for campaign timing</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Workspace ID</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>FK</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Filters visibility per tenant (ws9, ws10, cl1, cl2, etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>Intake / Referral / Website / Manual entry</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Implementation Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>• Likely needs a JSON schema file per tenant to define which fields are active/required (small firms may not need Bar Number, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>• Consider a lightweight web plugin/JSON config so agents (Elisa, backend-dev) can navigate the CRM contact structure quickly without hardcoding field names.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>• GDPR note: Marketing Consent field is mandatory for Italy-based clients (Romanelli, Pagliano) — do not enable bulk email without it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>• APPROVAL GATE: This table structure is approved as-is. Before Operator-Installer writes any code, backend-dev must submit an implementation plan (migration steps, affected files, rollback path) for sign-off.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Decisions Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Open and closed decisions, with rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Decision Item</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Decision / Answer</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Rationale / Next Step</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Matters (cases) cap per tenant</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>CLOSED — for now</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>No cap for now. Hermes must define HOW usage is tracked (dashboard/query) and AT WHAT threshold a limit gets set. Revisit at scale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Memory/storage cap per tenant</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>CLOSED — for now</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Same as above — tracked together, revisit when congestion signals appear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Seat limit per tenant</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>CLOSED — direction only</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Small limit (exact number TBD)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Start with a small limit per small-firm best practice. Operator-Installer to research and propose exact number (e.g. 3-5) for sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Internal vs client-facing contact models</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>CLOSED — approved as-is</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Two separate models</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>See Contact_Model sheet. Implementation plan required from backend-dev before coding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Elisa production access</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Read-only access during development; full production TBD</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>See Elisa_Rollout_Plan sheet for staged criteria and test plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Global 'local vs deployed' reporting rule</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Confirmed global, not just-this-once</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Applies to every future deploy/fix report, permanently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>RLS merge timing</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>OPEN — reminder only</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Do not merge until 18 tests pass on real Postgres + NOBYPASSRLS confirmed</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>No new deadline set; reminder persists in Delegation_Tracking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Ferro / AVIBE / aLEXy workspace confirmation</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Workspace IDs reportedly exist, unconfirmed</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Ask Hermes to confirm in inventory table — websites not linked, not tested yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>QA/Test-Debug agent adoption</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Identified candidate: QASkills.sh + debug skill</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Add to roster/Delegation_Tracking; not yet installed/activated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Memory-Curator agent for Obsidian vault</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>To be delegated by Operator-Installer</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Save tester-debugger profile/skills to working folders + Obsidian vault via memory-curator agent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Agentic AI-personalized email automation</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>OPEN — new item</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Not yet scoped</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>Add as new backlog item, separate from Contacts redesign.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Elisa (LexFlow PA) — Sandbox to Production Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Built by Stefano's dev pipeline, currently fully isolated</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Current State</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Elisa exists, generated and trained by Stefano's dev process. Lives in a fully isolated sandbox environment with NO access to real tenant data. This is the correct posture for an untested AI agent that will eventually read/write case data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Recommended Staged Access Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Data Access</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Approval Gate</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Test Method</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1">
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Stage 0 (current)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>None — fully isolated sandbox, synthetic/dummy data only</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>N/A — already in place</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Unit tests on synthetic case/contact data; verify no external API calls reach real DB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Read-only access to ONE non-critical test tenant (e.g. Pagliano or a dedicated Elisa-test workspace)</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Explicit approval from Olesia required before enabling</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Shadow mode: Elisa processes real read queries but her outputs are logged only, never shown to real users or written back</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1">
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Read-only across all test tenants (Romanelli, Pagliano, Ferro)</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Explicit approval, only after Stage 1 shows zero data leakage/errors for a defined period</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Parallel-run: compare Elisa's suggested actions against what a human would do manually; no autonomous writes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Write access, but ONLY within her own scoped actions (e.g. drafting reminders, not modifying case status)</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Explicit approval + human-in-the-loop confirmation required per write action initially</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Supervised writes: every write requires a one-click human confirm before committing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Stage 4 (production)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Full production access per her defined role</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Explicit final approval after Stage 3 track record reviewed</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Ongoing monitoring + audit log review; rollback plan defined before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Reasoning: Why Not Jump Straight to Read-Only Real Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>• Read-only access during early development IS acceptable in principle, but only inside a scoped, monitored test tenant — not general production data — because even read-only agents can leak data through logs, model outputs, or third-party API calls (e.g. if Elisa uses an external LLM API, real client data could leave your infrastructure).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>• Recommendation: create ONE dedicated 'Elisa-test' workspace with realistic but synthetic data first (Stage 0-1 boundary) before touching any real Romanelli/Pagliano/Ferro data — this fully de-risks the earliest testing phase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>• Only grant real tenant read access (Stage 1) once Elisa's data-handling (logging, retention, external API calls) has been audited by backend-dev — same audit discipline already applied to RLS/webhooks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>• Explicit production approval (Stage 4) should require: zero data incidents in Stage 1-3, a defined rollback/kill-switch, and sign-off from Olesia specifically — not automatic progression.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>